--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:57:11+00:00</t>
+    <t>2026-09-14T07:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:03:29+00:00</t>
+    <t>2026-09-14T07:11:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc4</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:11:51+00:00</t>
+    <t>2026-09-14T07:28:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:28:02+00:00</t>
+    <t>2026-09-14T08:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:01:31+00:00</t>
+    <t>2026-09-14T08:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:17:06+00:00</t>
+    <t>2026-10-09T09:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ci</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T09:59:07+00:00</t>
+    <t>2026-10-09T10:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:28:47+00:00</t>
+    <t>2026-10-09T10:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T10:42:14+00:00</t>
+    <t>2026-10-13T11:58:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T11:58:12+00:00</t>
+    <t>2026-10-13T12:04:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:04:10+00:00</t>
+    <t>2026-10-13T12:10:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:10:53+00:00</t>
+    <t>2026-10-13T12:17:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:17:17+00:00</t>
+    <t>2026-10-13T12:41:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
+++ b/StructureDefinition-mii-ex-labor-interpretationsbeeinflussende-eigenschaft.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:41:55+00:00</t>
+    <t>2026-10-13T13:04:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
